--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>46206</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,8 +1092,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1141,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1155,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1165,8 +1170,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1219,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1233,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1249,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1292,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1306,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44578</v>
+        <v>45600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1322,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1369,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1384,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1438,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1462,13 +1467,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,13 +1092,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1141,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1155,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46206</v>
+        <v>45077</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1170,13 +1165,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1233,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1309,7 +1299,7 @@
         <v>45600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1369,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1394,8 +1384,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1433,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1467,8 +1462,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44578</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45077</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1372,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1430,10 +1435,10 @@
       </c>
       <c r="V11" s="2" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1447,66 +1452,134 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>VADSTENA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 38484-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>ÖSTERGÖTLANDS LÄN</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,13 +1311,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1377,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1467,8 +1462,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1462,13 +1467,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1292,14 +1292,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,13 +1311,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1369,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1389,13 +1384,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1428,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1442,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1467,8 +1457,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1516,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>46206</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1540,8 +1535,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45077</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1292,14 +1292,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46282</v>
+        <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1384,8 +1384,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1445,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1506,7 +1511,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1516,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1535,13 +1540,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1372,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1433,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1443,14 +1448,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1462,13 +1467,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>44578</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44578</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>44578</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,13 +1311,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1377,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1438,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1448,14 +1443,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46282</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1467,8 +1462,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44578</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44578</v>
+        <v>45077</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45077</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1372,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1433,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1462,13 +1467,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1508,78 +1508,151 @@
       </c>
       <c r="V12" s="2" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
+          <t>A 41042-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VADSTENA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>A 38484-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>ÖSTERGÖTLANDS LÄN</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4.9</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1165,8 +1165,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1214,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1228,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,8 +1243,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1292,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1306,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46206</v>
+        <v>45600</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,13 +1321,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1389,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46282</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46206</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1165,13 +1165,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1214,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1228,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1243,13 +1238,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1292,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1306,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45600</v>
+        <v>44578</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1365,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1369,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1394,8 +1384,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1467,8 +1462,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45077</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46282</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44578</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>46282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>45077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44578</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>46206</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>46282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,8 +1019,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1068,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1082,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45600</v>
+        <v>46206</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,8 +1097,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1146,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1146,14 +1156,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>46282</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1176,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1219,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1219,14 +1229,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45077</v>
+        <v>46299</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1249,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1292,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1296,10 +1306,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44578</v>
+        <v>46305</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1312,7 +1322,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1355,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1369,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1384,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46206</v>
+        <v>45077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1462,13 +1467,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>45600</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1581,10 +1581,10 @@
       </c>
       <c r="V13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46282</v>
+        <v>45601</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,6 +1653,79 @@
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 50538-2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VADSTENA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,13 +1019,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1068,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46206</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1097,13 +1092,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1146,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1156,14 +1146,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46282</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1229,14 +1219,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>45600</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1292,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1306,10 +1296,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46305</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1321,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1365,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1394,8 +1389,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45077</v>
+        <v>44578</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45600</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45601</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1657,7 +1657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45601</v>
+        <v>46305</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44484</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1657,7 +1657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1667,14 +1667,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 57750-2021</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44484</v>
+        <v>45077</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1299,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1377,7 +1377,7 @@
         <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>A 42206-2026</t>
@@ -1601,7 +1601,7 @@
         <v>46305</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1653,79 +1653,6 @@
         <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 41042-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46299</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VADSTENA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45077</v>
+        <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,8 +1238,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1299,7 +1304,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1360,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1389,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,13 +1238,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1304,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1394,8 +1389,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45601</v>
+        <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,8 +1238,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1299,7 +1304,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1360,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1370,14 +1375,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1389,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46282</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,13 +1238,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1304,7 +1299,7 @@
         <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1365,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1375,14 +1370,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46282</v>
+        <v>46206</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1394,8 +1389,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1594,14 +1594,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>46206</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1165,8 +1165,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1214,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1228,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,8 +1243,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1282,7 +1292,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1292,14 +1302,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1311,13 +1321,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1360,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1389,13 +1394,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46282</v>
+        <v>46305</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46305</v>
+        <v>45077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45600</v>
+        <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,8 +1019,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1068,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 30143-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1082,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1092,8 +1097,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1146,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1146,14 +1156,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46206</v>
+        <v>46282</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1165,13 +1175,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1214,7 +1219,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1224,14 +1229,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46206</v>
+        <v>46299</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1243,13 +1248,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,14 +1302,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46282</v>
+        <v>46305</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44578</v>
+        <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46305</v>
+        <v>45077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1511,7 +1511,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1521,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45077</v>
+        <v>45600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>46206</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>46282</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>46299</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46305</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>46206</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>46206</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>46282</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>46299</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46305</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45601</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>45077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>45601</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45600</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AE13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44578</v>
+        <v>46206</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,8 +946,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +995,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1009,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46206</v>
+        <v>44578</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1019,13 +1024,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 30143-2026</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46206</v>
+        <v>45077</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1097,13 +1097,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1146,7 +1141,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1156,14 +1151,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46282</v>
+        <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1176,7 +1171,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,7 +1214,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1229,14 +1224,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1249,7 +1244,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1292,7 +1287,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1302,14 +1297,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46305</v>
+        <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1322,7 +1317,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1365,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45601</v>
+        <v>46305</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1395,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1438,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1452,10 +1447,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1468,7 +1463,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1508,10 +1503,10 @@
       </c>
       <c r="V12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1521,14 +1516,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45601</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1541,7 +1536,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1580,79 +1575,6 @@
         <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 50277-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45600</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VADSTENA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -946,13 +946,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -995,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1009,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44578</v>
+        <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1025,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1068,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45077</v>
+        <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1098,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1158,7 +1153,7 @@
         <v>45600</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1214,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1228,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1243,8 +1238,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1304,7 +1304,7 @@
         <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46305</v>
+        <v>44578</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 41042-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45601</v>
+        <v>46299</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41042-2026</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45601</v>
+        <v>45077</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45077</v>
+        <v>45600</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1080,7 +1080,7 @@
         <v>45601</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45600</v>
+        <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1226,7 +1226,7 @@
         <v>46206</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 42206-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44578</v>
+        <v>46305</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>46299</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42206-2026</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46305</v>
+        <v>44578</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>

--- a/Översikt VADSTENA.xlsx
+++ b/Översikt VADSTENA.xlsx
@@ -601,7 +601,7 @@
         <v>45077</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46167</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23678-2023</t>
+          <t>A 2253-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45077</v>
+        <v>44578</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 50277-2024</t>
+          <t>A 23678-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45600</v>
+        <v>45077</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 50530-2024</t>
+          <t>A 50277-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45601</v>
+        <v>45600</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 50538-2024</t>
+          <t>A 50530-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1153,7 +1153,7 @@
         <v>45601</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 30148-2026</t>
+          <t>A 50538-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46206</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1238,13 +1238,8 @@
           <t>VADSTENA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1287,7 +1282,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 38484-2026</t>
+          <t>A 30148-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1297,14 +1292,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46282</v>
+        <v>46206</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1316,8 +1311,13 @@
           <t>VADSTENA</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>46305</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>46299</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2253-2022</t>
+          <t>A 38484-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44578</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
